--- a/artfynd/A 50743-2024 artfynd.xlsx
+++ b/artfynd/A 50743-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121149723</v>
+        <v>121149726</v>
       </c>
       <c r="B2" t="n">
-        <v>91249</v>
+        <v>78338</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>760</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,14 +715,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ruskträsk, Ly lm</t>
+          <t>Rusksele, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>680270</v>
+        <v>680661</v>
       </c>
       <c r="R2" t="n">
-        <v>7196891</v>
+        <v>7196991</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121149726</v>
+        <v>121149723</v>
       </c>
       <c r="B3" t="n">
-        <v>78335</v>
+        <v>91259</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -826,14 +826,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rusksele, Ly lm</t>
+          <t>Ruskträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680661</v>
+        <v>680270</v>
       </c>
       <c r="R3" t="n">
-        <v>7196991</v>
+        <v>7196891</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -900,7 +900,7 @@
         <v>121149725</v>
       </c>
       <c r="B4" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 50743-2024 artfynd.xlsx
+++ b/artfynd/A 50743-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121149723</v>
+        <v>121149725</v>
       </c>
       <c r="B3" t="n">
-        <v>91259</v>
+        <v>79682</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -826,14 +826,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ruskträsk, Ly lm</t>
+          <t>Rusksele, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680270</v>
+        <v>680473</v>
       </c>
       <c r="R3" t="n">
-        <v>7196891</v>
+        <v>7197017</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121149725</v>
+        <v>121149723</v>
       </c>
       <c r="B4" t="n">
-        <v>79682</v>
+        <v>91259</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,14 +937,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rusksele, Ly lm</t>
+          <t>Ruskträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680473</v>
+        <v>680270</v>
       </c>
       <c r="R4" t="n">
-        <v>7197017</v>
+        <v>7196891</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 50743-2024 artfynd.xlsx
+++ b/artfynd/A 50743-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121149726</v>
       </c>
       <c r="B2" t="n">
-        <v>78338</v>
+        <v>78341</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121149725</v>
+        <v>121149723</v>
       </c>
       <c r="B3" t="n">
-        <v>79682</v>
+        <v>91271</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -826,14 +826,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rusksele, Ly lm</t>
+          <t>Ruskträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680473</v>
+        <v>680270</v>
       </c>
       <c r="R3" t="n">
-        <v>7197017</v>
+        <v>7196891</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121149723</v>
+        <v>121149725</v>
       </c>
       <c r="B4" t="n">
-        <v>91259</v>
+        <v>79685</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,14 +937,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ruskträsk, Ly lm</t>
+          <t>Rusksele, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680270</v>
+        <v>680473</v>
       </c>
       <c r="R4" t="n">
-        <v>7196891</v>
+        <v>7197017</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 50743-2024 artfynd.xlsx
+++ b/artfynd/A 50743-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>121149723</v>
       </c>
       <c r="B3" t="n">
-        <v>91271</v>
+        <v>91272</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 50743-2024 artfynd.xlsx
+++ b/artfynd/A 50743-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121149726</v>
+        <v>121149723</v>
       </c>
       <c r="B2" t="n">
-        <v>78341</v>
+        <v>91275</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,14 +715,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rusksele, Ly lm</t>
+          <t>Ruskträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>680661</v>
+        <v>680270</v>
       </c>
       <c r="R2" t="n">
-        <v>7196991</v>
+        <v>7196891</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121149723</v>
+        <v>121149725</v>
       </c>
       <c r="B3" t="n">
-        <v>91272</v>
+        <v>79688</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -826,14 +826,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ruskträsk, Ly lm</t>
+          <t>Rusksele, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680270</v>
+        <v>680473</v>
       </c>
       <c r="R3" t="n">
-        <v>7196891</v>
+        <v>7197017</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121149725</v>
+        <v>121149726</v>
       </c>
       <c r="B4" t="n">
-        <v>79685</v>
+        <v>78344</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680473</v>
+        <v>680661</v>
       </c>
       <c r="R4" t="n">
-        <v>7197017</v>
+        <v>7196991</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 50743-2024 artfynd.xlsx
+++ b/artfynd/A 50743-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121149723</v>
+        <v>121149726</v>
       </c>
       <c r="B2" t="n">
-        <v>91275</v>
+        <v>78344</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>760</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,14 +715,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ruskträsk, Ly lm</t>
+          <t>Rusksele, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>680270</v>
+        <v>680661</v>
       </c>
       <c r="R2" t="n">
-        <v>7196891</v>
+        <v>7196991</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121149725</v>
+        <v>121149723</v>
       </c>
       <c r="B3" t="n">
-        <v>79688</v>
+        <v>91275</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -826,14 +826,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rusksele, Ly lm</t>
+          <t>Ruskträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680473</v>
+        <v>680270</v>
       </c>
       <c r="R3" t="n">
-        <v>7197017</v>
+        <v>7196891</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121149726</v>
+        <v>121149725</v>
       </c>
       <c r="B4" t="n">
-        <v>78344</v>
+        <v>79688</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680661</v>
+        <v>680473</v>
       </c>
       <c r="R4" t="n">
-        <v>7196991</v>
+        <v>7197017</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
